--- a/Arbeitsrapport_ Projekt_Khalil's Gym.xlsx
+++ b/Arbeitsrapport_ Projekt_Khalil's Gym.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khalil Hamahmi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khalil Hamahmi\OneDrive - sluz\Dokumente\GitHub\IPT_4.1-Projekt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11EAF6A4-67BE-4199-986F-56937F555084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{859197BF-B928-488D-99EF-B5238FA08544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{0E4E67A2-2C85-46AE-B51D-DC0506011435}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
   <si>
     <t>Arbeitsplanung</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>20 Minuten</t>
+  </si>
+  <si>
+    <t>Data Grip mit Docker verbinden</t>
   </si>
 </sst>
 </file>
@@ -222,22 +225,6 @@
           <bgColor theme="4" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -330,26 +317,42 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border outline="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -365,14 +368,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2519006D-D796-4EA7-9E29-5BABF0AA95D3}" name="Tabelle1" displayName="Tabelle1" ref="C4:G24" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2519006D-D796-4EA7-9E29-5BABF0AA95D3}" name="Tabelle1" displayName="Tabelle1" ref="C4:G24" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
   <autoFilter ref="C4:G24" xr:uid="{2519006D-D796-4EA7-9E29-5BABF0AA95D3}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{F7731CB3-1A8C-4AF6-B212-55E05071D7C5}" name="Spalte1" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{56897F96-94D0-4BAA-B3B2-F50EF6FDA371}" name="Spalte2" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{8343EE31-3821-442F-A801-7D36824888B8}" name="Spalte3" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{E38A3F40-2F79-4C7A-A855-A71E622DDF3E}" name="Spalte4" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{BA291144-4D20-45FA-A0F2-97E31DFEC902}" name="Spalte5" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{F7731CB3-1A8C-4AF6-B212-55E05071D7C5}" name="Spalte1" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{56897F96-94D0-4BAA-B3B2-F50EF6FDA371}" name="Spalte2" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{8343EE31-3821-442F-A801-7D36824888B8}" name="Spalte3" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{E38A3F40-2F79-4C7A-A855-A71E622DDF3E}" name="Spalte4" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{BA291144-4D20-45FA-A0F2-97E31DFEC902}" name="Spalte5" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -835,10 +838,18 @@
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C12" s="3"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="C12" s="3">
+        <v>45989</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">

--- a/Arbeitsrapport_ Projekt_Khalil's Gym.xlsx
+++ b/Arbeitsrapport_ Projekt_Khalil's Gym.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khalil Hamahmi\OneDrive - sluz\Dokumente\GitHub\IPT_4.1-Projekt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{859197BF-B928-488D-99EF-B5238FA08544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8BC0DF1-4C65-40AD-8C19-FC5425E93E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{0E4E67A2-2C85-46AE-B51D-DC0506011435}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
   <si>
     <t>Arbeitsplanung</t>
   </si>
@@ -108,6 +108,12 @@
   </si>
   <si>
     <t>Data Grip mit Docker verbinden</t>
+  </si>
+  <si>
+    <t>Api erstellt und testdaten anzeigen</t>
+  </si>
+  <si>
+    <t>35 Minuten</t>
   </si>
 </sst>
 </file>
@@ -853,10 +859,18 @@
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C13" s="3"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="C13" s="3">
+        <v>45989</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">

--- a/Arbeitsrapport_ Projekt_Khalil's Gym.xlsx
+++ b/Arbeitsrapport_ Projekt_Khalil's Gym.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khalil Hamahmi\OneDrive - sluz\Dokumente\GitHub\IPT_4.1-Projekt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8BC0DF1-4C65-40AD-8C19-FC5425E93E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C8DB7B-637C-4D0E-9E0C-1CF61838ADBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{0E4E67A2-2C85-46AE-B51D-DC0506011435}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
   <si>
     <t>Arbeitsplanung</t>
   </si>
@@ -114,6 +114,21 @@
   </si>
   <si>
     <t>35 Minuten</t>
+  </si>
+  <si>
+    <t>Alle Testdaten anzeigen lassen</t>
+  </si>
+  <si>
+    <t>Views erstellen</t>
+  </si>
+  <si>
+    <t>10 Minuten</t>
+  </si>
+  <si>
+    <t>Routes für Views erstellen</t>
+  </si>
+  <si>
+    <t>15 Minuten</t>
   </si>
 </sst>
 </file>
@@ -874,24 +889,48 @@
       <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C14" s="3"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
+      <c r="C14" s="3">
+        <v>45996</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C15" s="3"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="C15" s="3">
+        <v>45996</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C16" s="3"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
+      <c r="C16" s="3">
+        <v>45996</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">

--- a/Arbeitsrapport_ Projekt_Khalil's Gym.xlsx
+++ b/Arbeitsrapport_ Projekt_Khalil's Gym.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khalil Hamahmi\OneDrive - sluz\Dokumente\GitHub\IPT_4.1-Projekt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C8DB7B-637C-4D0E-9E0C-1CF61838ADBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A22A17-94B7-4A93-8728-E2CEC0960DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{0E4E67A2-2C85-46AE-B51D-DC0506011435}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="33">
   <si>
     <t>Arbeitsplanung</t>
   </si>
@@ -129,6 +129,12 @@
   </si>
   <si>
     <t>15 Minuten</t>
+  </si>
+  <si>
+    <t>Routes mit View Verbinden/testen</t>
+  </si>
+  <si>
+    <t>40 Minuten</t>
   </si>
 </sst>
 </file>
@@ -934,10 +940,18 @@
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C17" s="3"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
+      <c r="C17" s="3">
+        <v>46003</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="G17" s="2"/>
     </row>
     <row r="18" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">

--- a/Arbeitsrapport_ Projekt_Khalil's Gym.xlsx
+++ b/Arbeitsrapport_ Projekt_Khalil's Gym.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khalil Hamahmi\OneDrive - sluz\Dokumente\GitHub\IPT_4.1-Projekt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A22A17-94B7-4A93-8728-E2CEC0960DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8373CB-6614-4CF2-97C3-FE25ACF07224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{0E4E67A2-2C85-46AE-B51D-DC0506011435}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
   <si>
     <t>Arbeitsplanung</t>
   </si>
@@ -135,6 +135,12 @@
   </si>
   <si>
     <t>40 Minuten</t>
+  </si>
+  <si>
+    <t>NavigationsBar Komponente</t>
+  </si>
+  <si>
+    <t>90 Minuten</t>
   </si>
 </sst>
 </file>
@@ -955,9 +961,15 @@
       <c r="G17" s="2"/>
     </row>
     <row r="18" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C18" s="3"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
+      <c r="C18" s="3">
+        <v>49662</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
     </row>

--- a/Arbeitsrapport_ Projekt_Khalil's Gym.xlsx
+++ b/Arbeitsrapport_ Projekt_Khalil's Gym.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khalil Hamahmi\OneDrive - sluz\Dokumente\GitHub\IPT_4.1-Projekt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8373CB-6614-4CF2-97C3-FE25ACF07224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95C9795-6CE2-4490-AC0D-62C9ABCD311C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{0E4E67A2-2C85-46AE-B51D-DC0506011435}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
   <si>
     <t>Arbeitsplanung</t>
   </si>
@@ -141,6 +141,12 @@
   </si>
   <si>
     <t>90 Minuten</t>
+  </si>
+  <si>
+    <t>StudioView</t>
+  </si>
+  <si>
+    <t>UnFin</t>
   </si>
 </sst>
 </file>
@@ -962,7 +968,7 @@
     </row>
     <row r="18" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
-        <v>49662</v>
+        <v>46010</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>33</v>
@@ -970,14 +976,24 @@
       <c r="E18" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F18" s="2"/>
+      <c r="F18" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="G18" s="2"/>
     </row>
     <row r="19" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C19" s="3"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
+      <c r="C19" s="3">
+        <v>46031</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="G19" s="2"/>
     </row>
     <row r="20" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
